--- a/ExtractorExcelToExcel/files_for_test/Data/Test_Input.xlsx
+++ b/ExtractorExcelToExcel/files_for_test/Data/Test_Input.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="148">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -565,9 +565,6 @@
   </si>
   <si>
     <t xml:space="preserve">Валин</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Id</t>
   </si>
 </sst>
 </file>
@@ -763,7 +760,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.69"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="21.6"/>
@@ -1117,7 +1114,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="8.21"/>
@@ -1658,8 +1655,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="8.21"/>
@@ -1667,11 +1664,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="22.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="19.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>56</v>
@@ -1687,6 +1686,9 @@
       </c>
       <c r="F1" s="6" t="s">
         <v>60</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1708,6 +1710,9 @@
       <c r="F2" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="H2" s="5" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -1728,6 +1733,7 @@
       <c r="F3" s="0" t="s">
         <v>69</v>
       </c>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1748,6 +1754,7 @@
       <c r="F4" s="0" t="s">
         <v>73</v>
       </c>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1768,6 +1775,7 @@
       <c r="F5" s="0" t="s">
         <v>78</v>
       </c>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1788,6 +1796,9 @@
       <c r="F6" s="0" t="s">
         <v>83</v>
       </c>
+      <c r="H6" s="5" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1808,6 +1819,7 @@
       <c r="F7" s="0" t="s">
         <v>78</v>
       </c>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1828,6 +1840,7 @@
       <c r="F8" s="0" t="s">
         <v>73</v>
       </c>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -1848,6 +1861,9 @@
       <c r="F9" s="0" t="s">
         <v>94</v>
       </c>
+      <c r="H9" s="5" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1868,6 +1884,7 @@
       <c r="F10" s="0" t="s">
         <v>69</v>
       </c>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1888,11 +1905,13 @@
       <c r="F11" s="0" t="s">
         <v>101</v>
       </c>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -1913,6 +1932,7 @@
       <c r="F13" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -1933,6 +1953,7 @@
       <c r="F14" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -1973,6 +1994,9 @@
       <c r="F16" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="H16" s="5" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2013,6 +2037,9 @@
       <c r="F18" s="0" t="s">
         <v>94</v>
       </c>
+      <c r="H18" s="5" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -2033,6 +2060,7 @@
       <c r="F19" s="0" t="s">
         <v>125</v>
       </c>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -2053,6 +2081,7 @@
       <c r="F20" s="0" t="s">
         <v>125</v>
       </c>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2073,6 +2102,7 @@
       <c r="F21" s="0" t="s">
         <v>73</v>
       </c>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -2093,11 +2123,13 @@
       <c r="F22" s="0" t="s">
         <v>73</v>
       </c>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -2118,6 +2150,7 @@
       <c r="F24" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">

--- a/ExtractorExcelToExcel/files_for_test/Data/Test_Input.xlsx
+++ b/ExtractorExcelToExcel/files_for_test/Data/Test_Input.xlsx
@@ -5,12 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Numéraux français" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Amino Acids" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="TestSheet" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="2 Rows Header" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="MultiIgnoring" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="152">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -321,6 +323,9 @@
     <t xml:space="preserve">hydrophobic</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t xml:space="preserve">Arg</t>
   </si>
   <si>
@@ -565,6 +570,45 @@
   </si>
   <si>
     <t xml:space="preserve">Валин</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">st</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> line of the header</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_</t>
   </si>
 </sst>
 </file>
@@ -574,7 +618,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -609,6 +653,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -653,7 +710,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -679,6 +736,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -760,7 +829,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultColWidth="11.9765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.69"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="21.6"/>
@@ -1114,7 +1183,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="8.21"/>
@@ -1167,6 +1236,9 @@
       <c r="F2" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="G2" s="0" t="s">
+        <v>66</v>
+      </c>
       <c r="H2" s="5" t="s">
         <v>63</v>
       </c>
@@ -1176,19 +1248,22 @@
         <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="F3" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1196,19 +1271,22 @@
         <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="F4" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1216,19 +1294,22 @@
         <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1236,22 +1317,25 @@
         <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1259,19 +1343,22 @@
         <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1279,19 +1366,22 @@
         <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="F8" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1299,22 +1389,25 @@
         <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>94</v>
+      <c r="F9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1322,19 +1415,22 @@
         <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="F10" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1342,19 +1438,22 @@
         <v>30</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="F11" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1362,19 +1461,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="F12" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1382,19 +1484,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1402,19 +1507,22 @@
         <v>15</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="F14" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1422,22 +1530,25 @@
         <v>5</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="G15" s="0" t="s">
+        <v>66</v>
+      </c>
       <c r="H15" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1445,19 +1556,22 @@
         <v>6</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H16" s="0"/>
     </row>
@@ -1466,22 +1580,25 @@
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="F17" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1489,19 +1606,22 @@
         <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D18" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="F18" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1509,19 +1629,22 @@
         <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F19" s="0" t="s">
-        <v>125</v>
+      <c r="G19" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1529,19 +1652,22 @@
         <v>9</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1549,19 +1675,22 @@
         <v>10</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1569,19 +1698,22 @@
         <v>8</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1589,19 +1721,22 @@
         <v>7</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1609,19 +1744,22 @@
         <v>2</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1630,9 +1768,6 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>51</v>
-      </c>
       <c r="B26" s="0"/>
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
@@ -1656,7 +1791,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="8.21"/>
@@ -1710,6 +1845,9 @@
       <c r="F2" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="G2" s="0" t="s">
+        <v>66</v>
+      </c>
       <c r="H2" s="5" t="s">
         <v>63</v>
       </c>
@@ -1719,19 +1857,22 @@
         <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="F3" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H3" s="5"/>
     </row>
@@ -1740,19 +1881,22 @@
         <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="F4" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H4" s="5"/>
     </row>
@@ -1761,19 +1905,22 @@
         <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H5" s="5"/>
     </row>
@@ -1782,22 +1929,25 @@
         <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1805,19 +1955,22 @@
         <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -1826,19 +1979,22 @@
         <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="F8" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -1847,22 +2003,25 @@
         <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="F9" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1870,19 +2029,22 @@
         <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="F10" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H10" s="5"/>
     </row>
@@ -1891,19 +2053,22 @@
         <v>30</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="F11" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H11" s="5"/>
     </row>
@@ -1911,6 +2076,9 @@
       <c r="A12" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="G12" s="0" t="s">
+        <v>66</v>
+      </c>
       <c r="H12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1918,19 +2086,22 @@
         <v>3</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H13" s="5"/>
     </row>
@@ -1939,19 +2110,22 @@
         <v>4</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H14" s="5"/>
     </row>
@@ -1960,19 +2134,22 @@
         <v>15</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="F15" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1980,22 +2157,25 @@
         <v>5</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>65</v>
       </c>
+      <c r="G16" s="0" t="s">
+        <v>66</v>
+      </c>
       <c r="H16" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2003,19 +2183,22 @@
         <v>6</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2023,22 +2206,25 @@
         <v>20</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D18" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="F18" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2046,19 +2232,22 @@
         <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="F19" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H19" s="5"/>
     </row>
@@ -2067,19 +2256,22 @@
         <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>125</v>
+      <c r="G20" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H20" s="5"/>
     </row>
@@ -2088,19 +2280,22 @@
         <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H21" s="5"/>
     </row>
@@ -2109,19 +2304,22 @@
         <v>10</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H22" s="5"/>
     </row>
@@ -2129,6 +2327,9 @@
       <c r="A23" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="G23" s="0" t="s">
+        <v>66</v>
+      </c>
       <c r="H23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2136,19 +2337,22 @@
         <v>8</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="H24" s="5"/>
     </row>
@@ -2157,19 +2361,22 @@
         <v>7</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2177,19 +2384,22 @@
         <v>2</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>65</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2215,4 +2425,1273 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="8.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="14.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="22.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="19.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="14.78"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0"/>
+      <c r="C27" s="0"/>
+      <c r="D27" s="0"/>
+      <c r="E27" s="0"/>
+      <c r="H27" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="8.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="14.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="22.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="19.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="14.78"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0"/>
+      <c r="C26" s="0"/>
+      <c r="D26" s="0"/>
+      <c r="E26" s="0"/>
+      <c r="H26" s="0"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>